--- a/data/mapping/adrg_mapping_template.xlsx
+++ b/data/mapping/adrg_mapping_template.xlsx
@@ -466,11 +466,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>전정기능의 장애</t>
+          <t>어깨 및 위팔의 골절</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -478,11 +478,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>발목을 포함한 아래다리의 골절</t>
+          <t>편도 및 아데노이드의 만성 질환</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -490,11 +490,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기타 세균성 장감염</t>
+          <t>비뇨계통의 기타 장애</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -502,11 +502,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>심방세동 및 조동</t>
+          <t>기타 추간판장애</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -514,11 +514,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>늑골, 흉골 및 흉추의 골절</t>
+          <t>만성 허혈심장병</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>여성생식관의 용종</t>
+          <t>어깨병변</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -538,11 +538,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>어깨 및 위팔의 골절</t>
+          <t>코 및 비동의 기타 장애</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -550,11 +550,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>편도 및 아데노이드의 만성 질환</t>
+          <t>발진티푸스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -562,11 +562,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아래팔의 골절</t>
+          <t>사타구니탈장</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -574,11 +574,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두개내손상</t>
+          <t>췌장의 악성 신생물</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -586,11 +586,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>기타 뇌혈관질환</t>
+          <t>급성 심근경색증</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -598,11 +598,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>비뇨계통의 기타 장애</t>
+          <t>대상포진</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -610,11 +610,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>장의 게실병</t>
+          <t>무릎의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -622,11 +622,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>기타 추간판장애</t>
+          <t>기타 척추병증</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -634,11 +634,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>만성 허혈심장병</t>
+          <t>장의 혈관장애</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -646,11 +646,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>탈장이 없는 마비성 장폐색증 및 장폐쇄</t>
+          <t>유방의 양성 신생물</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -658,11 +658,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>자궁의 평활근종</t>
+          <t>위궤양</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -670,11 +670,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>어깨병변</t>
+          <t>전립선의 악성 신생물</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -682,11 +682,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>일과성 뇌허혈발작 및 관련 증후군</t>
+          <t>팔의 단일신경병증</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -694,11 +694,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>기타 살모넬라감염</t>
+          <t>치핵 및 항문주위정맥혈전증</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -706,11 +706,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>기타 기능성 장장애</t>
+          <t>편도주위농양</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -718,11 +718,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>기타 염증성 간질환</t>
+          <t>담도의 기타 및 상세불명 부분의 악성 신생물</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -730,11 +730,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>발진티푸스</t>
+          <t>발작성 빈맥</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -742,11 +742,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>코 및 비동의 기타 장애</t>
+          <t>무릎의 내부장애</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -754,11 +754,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>사타구니탈장</t>
+          <t>기타 청력소실</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -766,11 +766,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>기타 및 부위불명의 소화계통의 양성 신생물</t>
+          <t>방광의 악성 신생물</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
@@ -778,11 +778,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>췌장의 악성 신생물</t>
+          <t>달리 분류되지 않은 바이러스폐렴</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -790,11 +790,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>급성 췌장염</t>
+          <t>유방의 제자리암종</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -802,11 +802,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>알코올성 간질환</t>
+          <t>동맥 및 세동맥의 기타 장애</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -814,11 +814,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>위의 악성 신생물</t>
+          <t>근육의 기타 장애</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
@@ -826,11 +826,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>급성 심근경색증</t>
+          <t>항뇌전증제, 진정제-수면제 및 항파킨슨제에 의한 중독</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -838,11 +838,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>전립선증식증</t>
+          <t>방광염</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -850,11 +850,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>수분, 전해질 및 산-염기균형의 기타 장애</t>
+          <t>급성 A형간염</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -862,11 +862,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>대상포진</t>
+          <t>기타 심장부정맥</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -874,11 +874,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>기타 패혈증</t>
+          <t>식도의 기타 질환</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -886,11 +886,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>무릎의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+          <t>단핵구성 백혈병</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
@@ -898,11 +898,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>뇌내출혈</t>
+          <t>상세불명의 혈뇨</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -910,11 +910,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>결장의 악성 신생물</t>
+          <t>기타 및 상세불명 부위의 양성 신생물</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
@@ -922,11 +922,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>기타 척추병증</t>
+          <t>자궁체부의 악성 신생물</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -934,11 +934,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>두개골 및 안면골의 골절</t>
+          <t>기타 특정 관절장애</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
@@ -946,11 +946,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>장의 혈관장애</t>
+          <t>골수형성이상증후군</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -958,11 +958,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>자궁내막증</t>
+          <t>이식장치의 조정 및 관리를 위하여 보건서비스와 접하고 있는 사람</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
@@ -970,11 +970,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>연조직염</t>
+          <t>윤활막 및 힘줄의 기타 장애</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -982,11 +982,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>유방의 양성 신생물</t>
+          <t>뇌전증</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -994,11 +994,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>위궤양</t>
+          <t>병적 골절을 동반한 골다공증</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -1006,11 +1006,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>발목을 제외한 발의 골절</t>
+          <t>달리 분류되지 않은 호흡부전</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
@@ -1018,11 +1018,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>팔의 단일신경병증</t>
+          <t>기타 및 상세불명의 원인에 의한 수막염</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -1030,11 +1030,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>전립선의 악성 신생물</t>
+          <t>기타 비감염성 위장염 및 결장염</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
@@ -1042,11 +1042,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>편도주위농양</t>
+          <t>기타 형태의 마이코박테리아에 의한 감염</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -1054,11 +1054,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>치핵 및 항문주위정맥혈전증</t>
+          <t>섬유모세포장애</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
@@ -1066,11 +1066,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>소화계통의 기타 질환</t>
+          <t>음낭수종 및 정액류</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -1078,11 +1078,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>수행되지 않은 특정 처치를 위해 보건서비스에 접하고 있는 사람</t>
+          <t>기타 비독성 고이터</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
@@ -1090,11 +1090,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>전립선의 염증성 질환</t>
+          <t>림프, 조혈 및 관련 조직의 행동양식 불명 및 미상의 기타 신생물</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -1102,11 +1102,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>담도의 기타 및 상세불명 부분의 악성 신생물</t>
+          <t>직장구불결장접합부의 악성 신생물</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
@@ -1114,11 +1114,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 처치의 합병증</t>
+          <t>유방의 기타 장애</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -1126,11 +1126,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>발작성 빈맥</t>
+          <t>기타 신세뇨관-간질질환</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
@@ -1138,11 +1138,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>복부 및 골반 통증</t>
+          <t>삼차신경의 장애</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -1150,11 +1150,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>내부 정형외과적 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+          <t>달리 분류되지 않은 간부전</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
@@ -1162,11 +1162,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>위 및 십이지장의 기타 질환</t>
+          <t>기타 내부 인공삽입장치, 삽입물 및 이식편의 합병증</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -1174,11 +1174,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>손목 및 손부위의 골절</t>
+          <t>질 및 외음부의 기타 염증</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
@@ -1186,11 +1186,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>무릎의 내부장애</t>
+          <t>연골의 기타 장애</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -1198,11 +1198,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>양성 지방종성 신생물</t>
+          <t>비뇨생식기 인공삽입장치, 삽입물 및 이식편의 합병증</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
@@ -1210,11 +1210,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>간 및 간내 담관의 악성 신생물</t>
+          <t>기타 윤활낭병증</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -1222,11 +1222,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>기타 청력소실</t>
+          <t>유방의 상세불명의 덩이</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
@@ -1234,11 +1234,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>난소의 양성 신생물</t>
+          <t>헤르페스바이러스[단순헤르페스] 감염</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -1246,11 +1246,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>방광의 악성 신생물</t>
+          <t>폐부종</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
@@ -1258,11 +1258,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>기타 급성 바이러스간염</t>
+          <t>비뇨 및 골반 기관의 손상</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -1270,11 +1270,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 바이러스폐렴</t>
+          <t>팔꿈치의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
@@ -1282,11 +1282,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>요추 및 골반의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+          <t>기타 말초혈관질환</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -1294,11 +1294,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>유방의 제자리암종</t>
+          <t>갑상선염</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
@@ -1306,11 +1306,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>간의 섬유증 및 경변증</t>
+          <t>복벽탈장</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -1318,11 +1318,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>기타 변형성 등병증</t>
+          <t>식품으로 섭취한 기타 유해물질의 독성효과</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
@@ -1330,11 +1330,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>여성생식기탈출</t>
+          <t>중이 및 호흡계통의 양성 신생물</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -1342,11 +1342,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>결합조직 및 기타 연조직의 기타 양성 신생물</t>
+          <t>항문 및 항문관의 악성 신생물</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
@@ -1354,11 +1354,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>동맥 및 세동맥의 기타 장애</t>
+          <t>기타 다발신경병증</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -1366,11 +1366,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 소화계통의 처치후 장애</t>
+          <t>기타 신체구조의 진단영상검사상 이상소견</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
@@ -1378,11 +1378,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>항뇌전증제, 진정제-수면제 및 항파킨슨제에 의한 중독</t>
+          <t>고관절의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
@@ -1390,11 +1390,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>방광염</t>
+          <t>뇌 및 중추신경계통의 행동양식 불명 또는 미상의 신생물</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -1402,11 +1402,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>근육의 기타 장애</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
@@ -1414,11 +1414,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>식도의 기타 질환</t>
+          <t>기타 골부착부병증</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -1426,11 +1426,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>기타 부위의 정맥류</t>
+          <t>발목 및 발 부위의 신경의 손상</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
@@ -1438,11 +1438,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>피부의 농양, 종기 및 큰종기</t>
+          <t>장의 기타 선천기형</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -1450,11 +1450,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>시각장애</t>
+          <t>사용, 과용 및 압박에 관련된 연조직장애</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
@@ -1462,11 +1462,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>기타 및 상세불명의 소화기관의 제자리암종</t>
+          <t>뇌의 기타 장애</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -1474,11 +1474,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>급성 A형간염</t>
+          <t>달리 분류되지 않은 귀의 기타 장애</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
@@ -1486,11 +1486,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>독성간질환</t>
+          <t>갑상선독증[갑상선기능항진증]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -1498,11 +1498,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>기타 심장부정맥</t>
+          <t>위공장궤양</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
@@ -1510,11 +1510,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>자궁경부의 이형성</t>
+          <t>출혈 또는 경색증으로 명시되지 않은 뇌졸중</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -1522,11 +1522,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>기타 및 부위불명 소화기관의 악성 신생물</t>
+          <t>달리 분류된 만성 질환에서의 빈혈</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
@@ -1534,11 +1534,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>복막염</t>
+          <t>기타 신경성 장애</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -1546,11 +1546,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>고환염 및 부고환염</t>
+          <t>유방의 비대</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
@@ -1558,11 +1558,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>상세불명의 혈뇨</t>
+          <t>복부, 아래등 및 골반 부위의 신경 및 허리척수의 손상</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -1570,11 +1570,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>기타 특정 관절장애</t>
+          <t>백혈구의 기타 장애</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
@@ -1582,11 +1582,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>골수형성이상증후군</t>
+          <t>상세불명의 비기질성 정신병</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -1594,11 +1594,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>방실차단 및 좌각차단</t>
+          <t>달리 분류된 질환에서의 신경계통의 기타 퇴행장애</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
@@ -1606,11 +1606,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>이식장치의 조정 및 관리를 위하여 보건서비스와 접하고 있는 사람</t>
+          <t>고환의 염전</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -1618,11 +1618,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>윤활막 및 힘줄의 기타 장애</t>
+          <t>기타 내부기관의 화상 및 부식</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
@@ -1630,11 +1630,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>기타 및 상세불명 부위의 이차성 악성 신생물</t>
+          <t>바이러스수막염</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -1642,11 +1642,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>구역 및 구토</t>
+          <t>림프절의 이차성 및 상세불명의 악성 신생물</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
